--- a/data/sed/clean/sed_2024_clean.xlsx
+++ b/data/sed/clean/sed_2024_clean.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="221">
   <si>
-    <t>s</t>
+    <t>Station</t>
   </si>
   <si>
     <t>Date</t>
